--- a/artfynd/A 206-2022 artfynd.xlsx
+++ b/artfynd/A 206-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121908924</v>
+        <v>121908926</v>
       </c>
       <c r="B2" t="n">
-        <v>57324</v>
+        <v>57744</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102621</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -715,7 +715,11 @@
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -795,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121908926</v>
+        <v>121908924</v>
       </c>
       <c r="B3" t="n">
-        <v>57744</v>
+        <v>57324</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,16 +815,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>102621</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -835,11 +839,7 @@
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
